--- a/site/leagues/betclic/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_CAB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_CAB.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F. Thomas (25 L)</t>
+          <t>F. Thomas (40 L)</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F. Thomas (14.0 3PA)</t>
+          <t>F. Thomas (24.0 3PA)</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F. Thomas (1.28)</t>
+          <t>F. Thomas (1.45)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Above the Break 3 (49 L)</t>
+          <t>Above the Break 3 (80 L)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Restricted Area (55.6%)</t>
+          <t>Restricted Area (65.2%)</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="17" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
@@ -589,7 +589,7 @@
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="20" customWidth="1" min="40" max="40"/>
     <col width="20" customWidth="1" min="41" max="41"/>
-    <col width="19" customWidth="1" min="42" max="42"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
     <col width="19" customWidth="1" min="45" max="45"/>
@@ -944,53 +944,53 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I2" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N2" t="n">
+        <v>24</v>
+      </c>
+      <c r="O2" t="n">
         <v>14</v>
       </c>
-      <c r="O2" t="n">
-        <v>6</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -1001,11 +1001,11 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1014,11 +1014,11 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1040,11 +1040,11 @@
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1053,11 +1053,11 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1079,11 +1079,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -1092,11 +1092,11 @@
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BA2" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1196,53 +1196,53 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I3" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1.08695652173913</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -1253,11 +1253,11 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1266,92 +1266,102 @@
         </is>
       </c>
       <c r="Y3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
         <v>6</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AB3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AK3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR3" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
         <v>6</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>4</v>
-      </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AV3" t="n">
@@ -1359,18 +1369,18 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY3" t="n">
         <v>3</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BA3" t="n">
@@ -1378,31 +1388,31 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
         <v>3</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -1438,53 +1448,53 @@
         </is>
       </c>
       <c r="G4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I4" t="n">
         <v>23</v>
       </c>
-      <c r="H4" t="n">
-        <v>7</v>
-      </c>
-      <c r="I4" t="n">
-        <v>18</v>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -1495,11 +1505,11 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1534,11 +1544,11 @@
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1563,11 +1573,11 @@
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1597,7 +1607,7 @@
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1605,7 +1615,7 @@
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY4" t="n">
         <v>2</v>
@@ -1616,22 +1626,22 @@
         </is>
       </c>
       <c r="BA4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>800.0%</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BD4" t="n">
         <v>2</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1640,7 +1650,7 @@
         </is>
       </c>
       <c r="BG4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
@@ -1680,112 +1690,122 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I5" t="n">
+        <v>27</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>21</v>
+      </c>
+      <c r="L5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>80.8%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1.038461538461539</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>11</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
         <v>7</v>
       </c>
-      <c r="I5" t="n">
-        <v>14</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>38.9%</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>14</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
         <v>7</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>9</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="Y5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
@@ -1795,37 +1815,37 @@
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AT5" t="n">
         <v>4</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
         <is>
           <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
       <c r="AV5" t="n">
@@ -1833,11 +1853,11 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY5" t="n">
         <v>6</v>
@@ -1852,27 +1872,27 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BD5" t="n">
         <v>6</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
@@ -1908,53 +1928,53 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="K6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" t="n">
         <v>6</v>
       </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>1.058823529411765</v>
+        <v>1.304347826086957</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1965,24 +1985,24 @@
         </is>
       </c>
       <c r="V6" t="n">
+        <v>10</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
         <v>8</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="Y6" t="n">
-        <v>6</v>
-      </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2004,24 +2024,24 @@
         </is>
       </c>
       <c r="AE6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
         <v>8</v>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AH6" t="n">
-        <v>6</v>
-      </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr"/>
@@ -2033,24 +2053,24 @@
         </is>
       </c>
       <c r="AN6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
         <v>8</v>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
-        <v>6</v>
-      </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2071,18 +2091,18 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BA6" t="n">
@@ -2090,31 +2110,31 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
           <t>300.0%</t>
         </is>
       </c>
-      <c r="BC6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BG6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -2150,32 +2170,32 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
         <v>10</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>31.2%</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2187,49 +2207,49 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0.625</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>7</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="V7" t="n">
-        <v>4</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="Y7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -2237,47 +2257,67 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AN7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
+      <c r="AQ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AT7" t="n">
@@ -2285,7 +2325,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AV7" t="n">
@@ -2293,18 +2333,18 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
         <v>5</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BA7" t="n">
@@ -2312,31 +2352,31 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>900.0%</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD7" t="n">
         <v>5</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BG7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -2372,28 +2412,28 @@
         </is>
       </c>
       <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
         <v>10</v>
       </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6</v>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -2409,16 +2449,16 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.6</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -2429,11 +2469,11 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -2462,9 +2502,19 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
@@ -2477,11 +2527,11 @@
         </is>
       </c>
       <c r="AN8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -2515,18 +2565,18 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BA8" t="n">
@@ -2534,31 +2584,31 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>800.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BC8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD8" t="n">
         <v>8</v>
       </c>
-      <c r="BD8" t="n">
-        <v>7</v>
-      </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BG8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2649,7 @@
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="17" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
@@ -2617,7 +2667,7 @@
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="20" customWidth="1" min="40" max="40"/>
     <col width="20" customWidth="1" min="41" max="41"/>
-    <col width="19" customWidth="1" min="42" max="42"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
     <col width="19" customWidth="1" min="45" max="45"/>
@@ -2972,53 +3022,53 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I2" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N2" t="n">
+        <v>24</v>
+      </c>
+      <c r="O2" t="n">
         <v>14</v>
       </c>
-      <c r="O2" t="n">
-        <v>6</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -3029,11 +3079,11 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -3042,11 +3092,11 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3068,11 +3118,11 @@
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -3081,11 +3131,11 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -3107,11 +3157,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -3120,11 +3170,11 @@
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -3156,7 +3206,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BA2" t="n">
@@ -3175,7 +3225,7 @@
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -3188,7 +3238,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3210,134 +3260,130 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>314650</t>
-        </is>
-      </c>
+          <t>CAB_G._SILVA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>G. Silva</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>23</v>
       </c>
       <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>30</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>52.2%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>14</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>39.1%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>60.9%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>1.304347826086957</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
         <v>10</v>
       </c>
-      <c r="I3" t="n">
-        <v>25</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>43.5%</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>11</v>
-      </c>
-      <c r="O3" t="n">
-        <v>5</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>52.2%</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>47.8%</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>1.08695652173913</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V3" t="n">
-        <v>9</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AE3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AB3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="AH3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr"/>
@@ -3349,41 +3395,41 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AV3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -3394,15 +3440,15 @@
         <v>2</v>
       </c>
       <c r="AY3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -3413,11 +3459,11 @@
         <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -3430,7 +3476,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -3452,130 +3498,134 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CAB_G._SILVA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>CAB_W._HEINZ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>316292</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>G. Silva</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" t="n">
+        <v>27</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>21</v>
+      </c>
+      <c r="L4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>80.8%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>1.038461538461539</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>11</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
         <v>7</v>
       </c>
-      <c r="I4" t="n">
-        <v>18</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>41.2%</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
         <v>11</v>
       </c>
-      <c r="O4" t="n">
-        <v>4</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35.3%</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>64.7%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>1.058823529411765</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>8</v>
-      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr"/>
@@ -3583,45 +3633,45 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AN4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
       <c r="AT4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -3632,15 +3682,15 @@
         <v>3</v>
       </c>
       <c r="AY4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -3651,11 +3701,11 @@
         <v>3</v>
       </c>
       <c r="BD4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -3668,7 +3718,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -3690,49 +3740,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>196210</t>
+          <t>314650</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I5" t="n">
+        <v>34</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>16</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>18</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>30.4%</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>11</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>12</v>
-      </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -3741,16 +3791,16 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.7826086956521739</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -3761,11 +3811,11 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -3774,11 +3824,11 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -3787,66 +3837,76 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
           <t>25.0%</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AE5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AN5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AH5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="AQ5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -3855,11 +3915,11 @@
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AV5" t="n">
@@ -3867,18 +3927,18 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="AX5" t="n">
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BA5" t="n">
@@ -3886,14 +3946,14 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BC5" t="n">
         <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -3902,7 +3962,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BG5" t="n">
@@ -3910,7 +3970,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -3932,38 +3992,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CAB_W._HEINZ</t>
+          <t>CAB_C._ROBERT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>316292</t>
+          <t>322686</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>W. Heinz</t>
+          <t>C. Robert</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -3971,7 +4031,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3983,16 +4043,16 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -4003,16 +4063,16 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -4020,33 +4080,33 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr"/>
@@ -4061,16 +4121,16 @@
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AQ6" t="n">
@@ -4078,24 +4138,24 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -4106,30 +4166,30 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
         <v>6</v>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>500.0%</t>
-        </is>
-      </c>
-      <c r="BA6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>5</v>
-      </c>
       <c r="BD6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -4142,7 +4202,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -4164,100 +4224,100 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CAB_N._SA</t>
+          <t>CAB_B._FERREIRA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>208207</t>
+          <t>196210</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>N. Sa</t>
+          <t>B. Ferreira</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>23</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>29.0%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>19</v>
+      </c>
+      <c r="O7" t="n">
         <v>5</v>
       </c>
-      <c r="I7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>31.2%</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>38.7%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>61.3%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>17</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
         <v>5</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>4</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="Y7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -4265,47 +4325,67 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AT7" t="n">
@@ -4313,41 +4393,41 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="AX7" t="n">
         <v>6</v>
       </c>
       <c r="AY7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BA7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>800.0%</t>
         </is>
       </c>
       <c r="BC7" t="n">
         <v>7</v>
       </c>
       <c r="BD7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -4356,7 +4436,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BG7" t="n">
@@ -4364,7 +4444,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
     </row>
@@ -4386,46 +4466,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CAB_C._ROBERT</t>
+          <t>CAB_N._SA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>322686</t>
+          <t>208207</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C. Robert</t>
+          <t>N. Sa</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>21</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>11</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
         <v>10</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4437,109 +4517,129 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>52.4%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>7</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>80.0%</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="V8" t="n">
-        <v>4</v>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="Y8" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
+      <c r="AH8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AN8" t="n">
+      <c r="AQ8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
         <v>4</v>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AQ8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AU8" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AT8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="AV8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -4550,30 +4650,30 @@
         <v>7</v>
       </c>
       <c r="AY8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BA8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>800.0%</t>
+          <t>900.0%</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -4586,7 +4686,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4727,7 @@
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="17" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
@@ -4645,7 +4745,7 @@
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="20" customWidth="1" min="40" max="40"/>
     <col width="20" customWidth="1" min="41" max="41"/>
-    <col width="19" customWidth="1" min="42" max="42"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
     <col width="19" customWidth="1" min="45" max="45"/>
@@ -5000,53 +5100,53 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I2" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N2" t="n">
+        <v>24</v>
+      </c>
+      <c r="O2" t="n">
         <v>14</v>
       </c>
-      <c r="O2" t="n">
-        <v>6</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -5057,11 +5157,11 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -5070,11 +5170,11 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5096,11 +5196,11 @@
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -5109,11 +5209,11 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -5135,11 +5235,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -5148,11 +5248,11 @@
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -5184,7 +5284,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BA2" t="n">
@@ -5203,7 +5303,7 @@
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -5216,7 +5316,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5252,53 +5352,53 @@
         </is>
       </c>
       <c r="G3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
         <v>23</v>
       </c>
-      <c r="H3" t="n">
-        <v>7</v>
-      </c>
-      <c r="I3" t="n">
-        <v>18</v>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -5309,11 +5409,11 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -5348,11 +5448,11 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -5377,11 +5477,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -5411,7 +5511,7 @@
         </is>
       </c>
       <c r="AV3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -5419,7 +5519,7 @@
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY3" t="n">
         <v>2</v>
@@ -5430,22 +5530,22 @@
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>800.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BD3" t="n">
         <v>2</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -5454,7 +5554,7 @@
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
@@ -5494,53 +5594,53 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1.08695652173913</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -5551,11 +5651,11 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -5564,92 +5664,102 @@
         </is>
       </c>
       <c r="Y4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
         <v>6</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AB4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AK4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
         <v>6</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>4</v>
-      </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AV4" t="n">
@@ -5657,18 +5767,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
         <v>3</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BA4" t="n">
@@ -5676,31 +5786,31 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
         <v>3</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BG4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -5732,53 +5842,53 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="K5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" t="n">
         <v>6</v>
       </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>1.058823529411765</v>
+        <v>1.304347826086957</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -5789,24 +5899,24 @@
         </is>
       </c>
       <c r="V5" t="n">
+        <v>10</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
         <v>8</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="Y5" t="n">
-        <v>6</v>
-      </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5828,24 +5938,24 @@
         </is>
       </c>
       <c r="AE5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
         <v>8</v>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AH5" t="n">
-        <v>6</v>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr"/>
@@ -5857,24 +5967,24 @@
         </is>
       </c>
       <c r="AN5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
         <v>8</v>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
-        <v>6</v>
-      </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -5895,18 +6005,18 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BA5" t="n">
@@ -5914,31 +6024,31 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
           <t>300.0%</t>
         </is>
       </c>
-      <c r="BC5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BG5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -5974,32 +6084,32 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
         <v>10</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>31.2%</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>10</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -6011,49 +6121,49 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.625</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>7</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="V6" t="n">
-        <v>4</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="Y6" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -6061,47 +6171,67 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AN6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
+      <c r="AQ6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AT6" t="n">
@@ -6109,7 +6239,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AV6" t="n">
@@ -6117,18 +6247,18 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>5</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BA6" t="n">
@@ -6136,31 +6266,31 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>900.0%</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD6" t="n">
         <v>5</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BG6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -6196,112 +6326,122 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H7" t="n">
+        <v>13</v>
+      </c>
+      <c r="I7" t="n">
+        <v>27</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>21</v>
+      </c>
+      <c r="L7" t="n">
+        <v>12</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>80.8%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>1.038461538461539</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>11</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
         <v>7</v>
       </c>
-      <c r="I7" t="n">
-        <v>14</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>38.9%</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>14</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
         <v>7</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>9</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="Y7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AE7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
@@ -6311,37 +6451,37 @@
         </is>
       </c>
       <c r="AN7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AT7" t="n">
         <v>4</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AU7" t="inlineStr">
         <is>
           <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
       <c r="AV7" t="n">
@@ -6349,11 +6489,11 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY7" t="n">
         <v>6</v>
@@ -6368,27 +6508,27 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BD7" t="n">
         <v>6</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BG7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
@@ -6428,28 +6568,28 @@
         </is>
       </c>
       <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
         <v>10</v>
       </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6</v>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -6465,16 +6605,16 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.6</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -6485,11 +6625,11 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -6518,9 +6658,19 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
@@ -6533,11 +6683,11 @@
         </is>
       </c>
       <c r="AN8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -6571,18 +6721,18 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BA8" t="n">
@@ -6590,31 +6740,31 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>800.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BC8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD8" t="n">
         <v>8</v>
       </c>
-      <c r="BD8" t="n">
-        <v>7</v>
-      </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BG8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7014,191 +7164,201 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_F._THOMAS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>314650</t>
+          <t>273176</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>F. Thomas</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
+        <v>22</v>
+      </c>
+      <c r="I2" t="n">
+        <v>58</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>16</v>
+      </c>
+      <c r="L2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>24</v>
+      </c>
+      <c r="O2" t="n">
+        <v>14</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>20</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
         <v>10</v>
       </c>
-      <c r="I2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>43.5%</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>12</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
         <v>5</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>11</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
         <v>5</v>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>52.2%</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>47.8%</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>1.08695652173913</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V2" t="n">
-        <v>9</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AN2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AB2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AH2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="AT2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AV2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
@@ -7206,18 +7366,18 @@
         </is>
       </c>
       <c r="BA2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -7226,11 +7386,11 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -7256,42 +7416,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>273176</t>
-        </is>
-      </c>
+          <t>CAB_G._SILVA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>G. Silva</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -7307,16 +7463,16 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1.28</v>
+        <v>1.304347826086957</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -7327,162 +7483,152 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AB3" t="n">
+      <c r="AH3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AV3" t="n">
         <v>5</v>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AH3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AK3" t="n">
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
         <v>5</v>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AV3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="BA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="BC3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="BG3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
@@ -7508,184 +7654,198 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CAB_G._SILVA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>CAB_M._TOMLEY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>314650</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>G. Silva</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>16</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
         <v>18</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>41.2%</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
+      <c r="O4" t="n">
         <v>6</v>
       </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>16</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>11</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AV4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
         <v>4</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35.3%</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>64.7%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>1.058823529411765</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AV4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>3</v>
       </c>
       <c r="AY4" t="n">
         <v>3</v>
@@ -7696,31 +7856,31 @@
         </is>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
         <v>3</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BG4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
@@ -7760,53 +7920,53 @@
         </is>
       </c>
       <c r="G5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
         <v>23</v>
       </c>
-      <c r="H5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>18</v>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -7817,11 +7977,11 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -7856,11 +8016,11 @@
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -7885,11 +8045,11 @@
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -7919,7 +8079,7 @@
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -7927,7 +8087,7 @@
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
         <v>2</v>
@@ -7938,35 +8098,277 @@
         </is>
       </c>
       <c r="BA5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>800.0%</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BD5" t="n">
         <v>2</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
           <t>400.0%</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CAB_N._SA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>208207</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>N. Sa</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>52.4%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>7</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>600.0%</t>
         </is>
       </c>
-      <c r="BG5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>400.0%</t>
+      <c r="BA6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>900.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -8136,21 +8538,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.7959183673469388</v>
+        <v>0.975</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -8159,14 +8561,14 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="M2" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -8185,7 +8587,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -8219,27 +8621,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.111111111111111</v>
+        <v>1.304347826086957</v>
       </c>
       <c r="J3" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -8249,7 +8651,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -8268,7 +8670,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -8302,27 +8704,27 @@
         </is>
       </c>
       <c r="E4" t="n">
+        <v>33</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="n">
         <v>24</v>
       </c>
-      <c r="F4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G4" t="n">
-        <v>14</v>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -8332,7 +8734,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -8351,7 +8753,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -8385,27 +8787,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -8415,7 +8817,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -8468,7 +8870,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -8478,11 +8880,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -8491,25 +8893,25 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M6" t="n">
         <v>3</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>5</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -8517,11 +8919,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>400.0%</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8545,21 +8953,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.25</v>
+        <v>1.875</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -8568,14 +8976,14 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -8586,7 +8994,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -8594,7 +9002,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -8611,7 +9019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8766,27 +9174,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.111111111111111</v>
+        <v>1.304347826086957</v>
       </c>
       <c r="J2" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -8796,7 +9204,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -8815,7 +9223,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -8849,27 +9257,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -8879,7 +9287,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -8932,27 +9340,27 @@
         </is>
       </c>
       <c r="E4" t="n">
+        <v>33</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="n">
         <v>24</v>
       </c>
-      <c r="F4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G4" t="n">
-        <v>14</v>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -8962,7 +9370,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -8981,7 +9389,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -9015,21 +9423,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.7959183673469388</v>
+        <v>0.975</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -9038,14 +9446,14 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="M5" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -9064,15 +9472,98 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5.0%</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>600.0%</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>400.0%</t>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X11"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9275,21 +9766,21 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.363636363636364</v>
+        <v>1.8</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -9298,14 +9789,14 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -9316,23 +9807,23 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>300.0%</t>
         </is>
       </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -9373,21 +9864,21 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.9</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -9396,14 +9887,14 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -9422,7 +9913,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -9452,56 +9943,56 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CAB_W._HEINZ</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>316292</t>
+          <t>314650</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>W. Heinz</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.111111111111111</v>
+        <v>0.75</v>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -9512,7 +10003,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -9520,7 +10011,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -9528,7 +10019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -9550,56 +10041,56 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>314650</t>
+          <t>316292</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" t="n">
-        <v>9</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3</v>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -9610,23 +10101,23 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>500.0%</t>
-        </is>
-      </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -9663,21 +10154,21 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -9686,14 +10177,14 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -9712,7 +10203,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -9761,7 +10252,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -9771,14 +10262,14 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -9791,7 +10282,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -9802,7 +10293,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="U7" t="n">
@@ -9810,7 +10301,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -9818,7 +10309,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -9855,27 +10346,27 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9885,7 +10376,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="R8" t="n">
@@ -9904,7 +10395,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -9953,13 +10444,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -9970,10 +10461,10 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -9983,7 +10474,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="R9" t="n">
@@ -9994,7 +10485,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="U9" t="n">
@@ -10002,7 +10493,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="W9" t="n">
@@ -10010,7 +10501,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -10032,26 +10523,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>273176</t>
+          <t>316292</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
@@ -10061,14 +10552,14 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.6</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
@@ -10081,34 +10572,34 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -10130,81 +10621,571 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_N._SA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>196210</t>
+          <t>208207</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>N. Sa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CAB_C._ROBERT</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>322686</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>C. Robert</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CAB_M._TOMLEY</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>314650</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>M. Tomley</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>17.6%</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>3</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CAB_F._THOMAS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>273176</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>F. Thomas</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>3</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CAB_N._SA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>208207</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>N. Sa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>23.8%</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CAB_B._FERREIRA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>196210</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>B. Ferreira</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="U11" t="n">
+      <c r="U16" t="n">
         <v>2</v>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>500.0%</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="W16" t="n">
         <v>2</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>200.0%</t>
         </is>
@@ -10221,7 +11202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10409,27 +11390,27 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.111111111111111</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -10439,7 +11420,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -10458,7 +11439,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -10488,83 +11469,79 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>273176</t>
-        </is>
-      </c>
+          <t>CAB_G._SILVA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>G. Silva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
         <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.363636363636364</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
-        <v>11</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5</v>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>300.0%</t>
         </is>
       </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -10586,17 +11563,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_F._THOMAS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>314650</t>
+          <t>273176</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>F. Thomas</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -10605,21 +11582,21 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -10628,14 +11605,14 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -10654,7 +11631,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -10684,83 +11661,83 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>196210</t>
+          <t>314650</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
+        <v>8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" t="n">
-        <v>10</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3</v>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -10797,21 +11774,21 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -10820,41 +11797,335 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>43.5%</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CAB_F._THOMAS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>273176</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>F. Thomas</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CAB_M._TOMLEY</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>314650</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>M. Tomley</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>16</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>16</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>47.1%</t>
         </is>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>300.0%</t>
         </is>
       </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>200.0%</t>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CAB_B._FERREIRA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>196210</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>B. Ferreira</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>17</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>17</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>54.8%</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
